--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/3591-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/3591-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{163ADD5F-DEC1-4FF8-BC5C-7AAC4E32E904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A31294DF-26E2-434C-B53B-DA25AE6FD264}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{132D9643-7D1D-46DF-90DF-7AB57FAD1BAA}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{497811DB-5A06-4BF9-AEDF-8708D910A082}"/>
   </bookViews>
   <sheets>
     <sheet name="3591-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1457,27 +1457,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E94322C7-FC5A-4845-949A-9F19347969DF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81457151-A87D-4BB7-AE4B-89962A906D77}">
   <dimension ref="A1:X23"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="6" width="6.25" customWidth="1"/>
-    <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1511,7 +1510,7 @@
       <c r="W1" s="26"/>
       <c r="X1" s="18"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
@@ -1547,7 +1546,7 @@
       <c r="W2" s="28"/>
       <c r="X2" s="29"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
         <v>2</v>
       </c>
@@ -1599,7 +1598,7 @@
       </c>
       <c r="X3" s="32"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="21"/>
       <c r="B4" s="22"/>
       <c r="C4" s="7"/>
@@ -1667,7 +1666,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="33">
         <v>2024</v>
       </c>
@@ -1739,7 +1738,7 @@
         <v>4.42</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="35">
         <v>2023</v>
       </c>
@@ -1811,7 +1810,7 @@
         <v>2.37</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="33">
         <v>2022</v>
       </c>
@@ -1883,7 +1882,7 @@
         <v>1.92</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="35">
         <v>2021</v>
       </c>
@@ -1955,7 +1954,7 @@
         <v>6.38</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="33">
         <v>2020</v>
       </c>
@@ -2027,7 +2026,7 @@
         <v>1.99</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>2019</v>
       </c>
@@ -2099,7 +2098,7 @@
         <v>1.36</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="33">
         <v>2018</v>
       </c>
@@ -2171,7 +2170,7 @@
         <v>2.46</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="35">
         <v>2017</v>
       </c>
@@ -2243,7 +2242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="33">
         <v>2016</v>
       </c>
@@ -2315,7 +2314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="35">
         <v>2015</v>
       </c>
@@ -2387,7 +2386,7 @@
         <v>2.92</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="33">
         <v>2014</v>
       </c>
@@ -2459,7 +2458,7 @@
         <v>1.92</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="35">
         <v>2013</v>
       </c>
@@ -2531,7 +2530,7 @@
         <v>2.02</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="33">
         <v>2012</v>
       </c>
@@ -2603,7 +2602,7 @@
         <v>2.95</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="35">
         <v>2011</v>
       </c>
@@ -2675,7 +2674,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="33">
         <v>2010</v>
       </c>
@@ -2747,7 +2746,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="35">
         <v>2009</v>
       </c>
@@ -2819,7 +2818,7 @@
         <v>4.29</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="33">
         <v>2008</v>
       </c>
@@ -2891,7 +2890,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="35">
         <v>2007</v>
       </c>
@@ -2963,7 +2962,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="33" t="s">
         <v>45</v>
       </c>
